--- a/审核导出/uv_oil_matte_审核.xlsx
+++ b/审核导出/uv_oil_matte_审核.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1.功能与AM-8828UV油相同(僅氣味降低) / 2.針對低氣味要求客戶產品使用(對氣味敏感客戶PENGUIN BOOKS使用)，如S1736550&lt;PP豬白板筆膠袋套裝(6本)&gt;工程客人</t>
+          <t>1.功能與AM-8828UV油相同(僅氣味降低) / 2.針對低氣味要求客戶產品使用(對氣味敏感客戶PENGUIN BOOKS使用)，如S1736550&lt;PP豬白板筆膠袋套裝(6本)&gt;工程客人</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>針對用於： / 1)平裝書封面過UV油 / 2)扇形/風琴咭書類過UV工程如S1503325&lt;&lt;藍色之旅&gt;&gt; / 3)針對防爆色要求高的工程如S1508343&lt;&lt;趣味滑道咭書&gt;&gt; / 4)針對過UV咭書產品用紙為啤線爆色數據為預警、高危，需過防爆色UV底油PC-8061(離線)； / 4)揭頁/沖床咭書需過防爆色UV底油PC-8061(離線)；</t>
+          <t>針對用於： / 1)平裝書封面過UV油 / 2)扇形/風琴咭書類過UV工程如S1503325&lt;&lt;藍色之旅&gt;&gt; / 3)針對防爆色要求高的工程如S1508343&lt;&lt;趣味滑道咭書&gt;&gt; / 4)針對過UV咭書產品用紙為啤線爆色數據為預警、高危，需過防爆色UV底油PC-8061(離線)； / 4)揭頁/沖牀咭書需過防爆色UV底油PC-8061(離線)；</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>离線抗爆線底油</t>
+          <t>離線抗爆線底油</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金</t>
+          <t>立體擊凸</t>
         </is>
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
-          <t>立體擊凸</t>
+          <t>立體燙金</t>
         </is>
       </c>
       <c r="X1" s="3" t="inlineStr">
@@ -1534,14 +1534,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W2" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V2" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X2" s="5" t="inlineStr">
@@ -1902,14 +1902,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W3" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X3" s="5" t="inlineStr">
@@ -2270,14 +2270,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W4" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X4" s="5" t="inlineStr">
@@ -3006,14 +3006,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W6" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X6" s="5" t="inlineStr">
@@ -3374,14 +3374,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W7" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X7" s="5" t="inlineStr">
@@ -4478,14 +4478,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W10" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V10" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X10" s="5" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>离線抗爆線底油</t>
+          <t>離線抗爆線底油</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -5950,14 +5950,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W14" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X14" s="5" t="inlineStr">
